--- a/artifacts/interface.xlsx
+++ b/artifacts/interface.xlsx
@@ -876,10 +876,12 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: artifacts/interface.md (src/coordinator/app.py 와 대조해 맞춘 명세서). 같은 내용을 인터페이스별 시트로 나눠 담았고, 항목 수는 각 시트에 실제로 들어간 행 수다. 값은 수식 없이 그대로 적었다.</t>
+          <t xml:space="preserve">출처: artifacts/interface.md (src/coordinator/app.py 와 대조한 명세서). 인터페이스별 시트에 수식 없이 값을 기록했다.
+공통 오류: 도메인 검증 422는 {error_code, message}, 요청 스키마 검증 422는 {detail: [{loc, msg, type, ...}]}이다. 그 밖의 오류는 detail 문자열을 반환한다.
+UNSAFE_PARTITION_PREDICATE: 분할 IN이 WHERE의 필수 양의 조건이 아니어서 거절했다. OR·NOT·값 표현식 안의 IN은 분할할 수 없다.</t>
         </is>
       </c>
     </row>
